--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260701.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260701.xlsx
@@ -2692,7 +2692,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-01 08:04</t>
+          <t>Generated: 2026-07-01 22:49</t>
         </is>
       </c>
     </row>
